--- a/relatorios/quadro-visitas/Quadro_Visitas_Vigna_02062024.xlsx
+++ b/relatorios/quadro-visitas/Quadro_Visitas_Vigna_02062024.xlsx
@@ -71,7 +71,9 @@
   </si>
   <si>
     <t xml:space="preserve">① Gestão de Riscos Psicossociais NR-1 (Compliance Control)
-② Compliance Trabalhista (Vigna Advogados)</t>
+② Compliance Trabalhista (Vigna Advogados)
+Pauta: Sistema Compliance NR1+
+Link: Reunião via Microsoft Teams</t>
   </si>
   <si>
     <t>Documento confidencial · Uso interno · Grupo Vigna © 2026</t>
